--- a/마일리지_할인_계산기.xlsx
+++ b/마일리지_할인_계산기.xlsx
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$B$4)+1)))</f>
+        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$B$4)+1)))</f>
         <v/>
       </c>
       <c r="C8" s="4">
-        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$H$2:$H$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$B$4)+1)))</f>
+        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$H$2:$H$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$B$4)+1)))</f>
         <v/>
       </c>
       <c r="D8" s="6">
@@ -634,11 +634,11 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$B$4)+1)))</f>
+        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$B$4)+1)))</f>
         <v/>
       </c>
       <c r="C9" s="4">
-        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$H$32:$H$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$B$4)+1)))</f>
+        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$H$32:$H$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$B$4)+1)))</f>
         <v/>
       </c>
       <c r="D9" s="6">
@@ -681,11 +681,11 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$B$4)+1)))</f>
+        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$B$4)+1)))</f>
         <v/>
       </c>
       <c r="C10" s="4">
-        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$H$122:$H$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$B$4)+1)))</f>
+        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$H$122:$H$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$B$4)+1)))</f>
         <v/>
       </c>
       <c r="D10" s="6">
@@ -728,11 +728,11 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$B$4)+1)))</f>
+        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$B$4)+1)))</f>
         <v/>
       </c>
       <c r="C11" s="4">
-        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$H$178:$H$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$B$4)+1)))</f>
+        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$H$178:$H$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$B$4)+1)))</f>
         <v/>
       </c>
       <c r="D11" s="6">
@@ -775,11 +775,11 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$B$4)+1)))</f>
+        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$B$4)+1)))</f>
         <v/>
       </c>
       <c r="C12" s="4">
-        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$H$424:$H$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$B$4)+1)))</f>
+        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$H$424:$H$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$B$4)+1)))</f>
         <v/>
       </c>
       <c r="D12" s="6">
@@ -822,11 +822,11 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$B$4)+1)))</f>
+        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$B$4)+1)))</f>
         <v/>
       </c>
       <c r="C13" s="4">
-        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$H$451:$H$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$B$4)+1)))</f>
+        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$H$451:$H$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$B$4)+1)))</f>
         <v/>
       </c>
       <c r="D13" s="6">
@@ -869,11 +869,11 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$B$4)+1)))</f>
+        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$B$4)+1)))</f>
         <v/>
       </c>
       <c r="C14" s="4">
-        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$H$458:$H$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$B$4)+1)))</f>
+        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$H$458:$H$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$B$4)+1)))</f>
         <v/>
       </c>
       <c r="D14" s="6">
@@ -916,11 +916,11 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$B$4)+1)))</f>
+        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$B$4)+1)))</f>
         <v/>
       </c>
       <c r="C15" s="4">
-        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$H$474:$H$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$B$4)+1)))</f>
+        <f>IF(OR($B$4="",NOT(ISNUMBER($B$4)),$B$4&lt;0),"",IF($B$4&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$H$474:$H$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$B$4)+1)))</f>
         <v/>
       </c>
       <c r="D15" s="6">
@@ -1221,35 +1221,35 @@
         <v>1000</v>
       </c>
       <c r="B4">
-        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A4)+1)))</f>
+        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A4)+1)))</f>
         <v/>
       </c>
       <c r="C4">
-        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A4)+1)))</f>
+        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A4)+1)))</f>
         <v/>
       </c>
       <c r="D4">
-        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A4)+1)))</f>
+        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A4)+1)))</f>
         <v/>
       </c>
       <c r="E4">
-        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A4)+1)))</f>
+        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A4)+1)))</f>
         <v/>
       </c>
       <c r="F4">
-        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A4)+1)))</f>
+        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A4)+1)))</f>
         <v/>
       </c>
       <c r="G4">
-        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A4)+1)))</f>
+        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A4)+1)))</f>
         <v/>
       </c>
       <c r="H4">
-        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A4)+1)))</f>
+        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A4)+1)))</f>
         <v/>
       </c>
       <c r="I4">
-        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A4)+1)))</f>
+        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A4)+1)))</f>
         <v/>
       </c>
       <c r="J4" t="inlineStr">
@@ -1267,35 +1267,35 @@
         <v>2500</v>
       </c>
       <c r="B5">
-        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A5)+1)))</f>
+        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A5)+1)))</f>
         <v/>
       </c>
       <c r="C5">
-        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A5)+1)))</f>
+        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A5)+1)))</f>
         <v/>
       </c>
       <c r="D5">
-        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A5)+1)))</f>
+        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A5)+1)))</f>
         <v/>
       </c>
       <c r="E5">
-        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A5)+1)))</f>
+        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A5)+1)))</f>
         <v/>
       </c>
       <c r="F5">
-        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A5)+1)))</f>
+        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A5)+1)))</f>
         <v/>
       </c>
       <c r="G5">
-        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A5)+1)))</f>
+        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A5)+1)))</f>
         <v/>
       </c>
       <c r="H5">
-        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A5)+1)))</f>
+        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A5)+1)))</f>
         <v/>
       </c>
       <c r="I5">
-        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A5)+1)))</f>
+        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A5)+1)))</f>
         <v/>
       </c>
       <c r="J5" t="inlineStr">
@@ -1313,35 +1313,35 @@
         <v>3000</v>
       </c>
       <c r="B6">
-        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A6)+1)))</f>
+        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A6)+1)))</f>
         <v/>
       </c>
       <c r="C6">
-        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A6)+1)))</f>
+        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A6)+1)))</f>
         <v/>
       </c>
       <c r="D6">
-        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A6)+1)))</f>
+        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A6)+1)))</f>
         <v/>
       </c>
       <c r="E6">
-        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A6)+1)))</f>
+        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A6)+1)))</f>
         <v/>
       </c>
       <c r="F6">
-        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A6)+1)))</f>
+        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A6)+1)))</f>
         <v/>
       </c>
       <c r="G6">
-        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A6)+1)))</f>
+        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A6)+1)))</f>
         <v/>
       </c>
       <c r="H6">
-        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A6)+1)))</f>
+        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A6)+1)))</f>
         <v/>
       </c>
       <c r="I6">
-        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A6)+1)))</f>
+        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A6)+1)))</f>
         <v/>
       </c>
       <c r="J6" t="inlineStr">
@@ -1359,35 +1359,35 @@
         <v>4500</v>
       </c>
       <c r="B7">
-        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A7)+1)))</f>
+        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A7)+1)))</f>
         <v/>
       </c>
       <c r="C7">
-        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A7)+1)))</f>
+        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A7)+1)))</f>
         <v/>
       </c>
       <c r="D7">
-        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A7)+1)))</f>
+        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A7)+1)))</f>
         <v/>
       </c>
       <c r="E7">
-        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A7)+1)))</f>
+        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A7)+1)))</f>
         <v/>
       </c>
       <c r="F7">
-        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A7)+1)))</f>
+        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A7)+1)))</f>
         <v/>
       </c>
       <c r="G7">
-        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A7)+1)))</f>
+        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A7)+1)))</f>
         <v/>
       </c>
       <c r="H7">
-        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A7)+1)))</f>
+        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A7)+1)))</f>
         <v/>
       </c>
       <c r="I7">
-        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A7)+1)))</f>
+        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A7)+1)))</f>
         <v/>
       </c>
       <c r="J7" t="inlineStr">
@@ -1405,35 +1405,35 @@
         <v>5000</v>
       </c>
       <c r="B8">
-        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A8)+1)))</f>
+        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A8)+1)))</f>
         <v/>
       </c>
       <c r="C8">
-        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A8)+1)))</f>
+        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A8)+1)))</f>
         <v/>
       </c>
       <c r="D8">
-        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A8)+1)))</f>
+        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A8)+1)))</f>
         <v/>
       </c>
       <c r="E8">
-        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A8)+1)))</f>
+        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A8)+1)))</f>
         <v/>
       </c>
       <c r="F8">
-        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A8)+1)))</f>
+        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A8)+1)))</f>
         <v/>
       </c>
       <c r="G8">
-        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A8)+1)))</f>
+        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A8)+1)))</f>
         <v/>
       </c>
       <c r="H8">
-        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A8)+1)))</f>
+        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A8)+1)))</f>
         <v/>
       </c>
       <c r="I8">
-        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A8)+1)))</f>
+        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A8)+1)))</f>
         <v/>
       </c>
       <c r="J8" t="inlineStr">
@@ -1451,35 +1451,35 @@
         <v>7000</v>
       </c>
       <c r="B9">
-        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A9)+1)))</f>
+        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A9)+1)))</f>
         <v/>
       </c>
       <c r="C9">
-        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A9)+1)))</f>
+        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A9)+1)))</f>
         <v/>
       </c>
       <c r="D9">
-        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A9)+1)))</f>
+        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A9)+1)))</f>
         <v/>
       </c>
       <c r="E9">
-        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A9)+1)))</f>
+        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A9)+1)))</f>
         <v/>
       </c>
       <c r="F9">
-        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A9)+1)))</f>
+        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A9)+1)))</f>
         <v/>
       </c>
       <c r="G9">
-        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A9)+1)))</f>
+        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A9)+1)))</f>
         <v/>
       </c>
       <c r="H9">
-        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A9)+1)))</f>
+        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A9)+1)))</f>
         <v/>
       </c>
       <c r="I9">
-        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A9)+1)))</f>
+        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A9)+1)))</f>
         <v/>
       </c>
       <c r="J9" t="inlineStr">
@@ -1497,35 +1497,35 @@
         <v>9000</v>
       </c>
       <c r="B10">
-        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A10)+1)))</f>
+        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A10)+1)))</f>
         <v/>
       </c>
       <c r="C10">
-        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A10)+1)))</f>
+        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A10)+1)))</f>
         <v/>
       </c>
       <c r="D10">
-        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A10)+1)))</f>
+        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A10)+1)))</f>
         <v/>
       </c>
       <c r="E10">
-        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A10)+1)))</f>
+        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A10)+1)))</f>
         <v/>
       </c>
       <c r="F10">
-        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A10)+1)))</f>
+        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A10)+1)))</f>
         <v/>
       </c>
       <c r="G10">
-        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A10)+1)))</f>
+        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A10)+1)))</f>
         <v/>
       </c>
       <c r="H10">
-        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A10)+1)))</f>
+        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A10)+1)))</f>
         <v/>
       </c>
       <c r="I10">
-        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A10)+1)))</f>
+        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A10)+1)))</f>
         <v/>
       </c>
       <c r="J10" t="inlineStr">
@@ -1543,35 +1543,35 @@
         <v>11000</v>
       </c>
       <c r="B11">
-        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A11)+1)))</f>
+        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A11)+1)))</f>
         <v/>
       </c>
       <c r="C11">
-        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A11)+1)))</f>
+        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A11)+1)))</f>
         <v/>
       </c>
       <c r="D11">
-        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A11)+1)))</f>
+        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A11)+1)))</f>
         <v/>
       </c>
       <c r="E11">
-        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A11)+1)))</f>
+        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A11)+1)))</f>
         <v/>
       </c>
       <c r="F11">
-        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A11)+1)))</f>
+        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A11)+1)))</f>
         <v/>
       </c>
       <c r="G11">
-        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A11)+1)))</f>
+        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A11)+1)))</f>
         <v/>
       </c>
       <c r="H11">
-        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A11)+1)))</f>
+        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A11)+1)))</f>
         <v/>
       </c>
       <c r="I11">
-        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A11)+1)))</f>
+        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A11)+1)))</f>
         <v/>
       </c>
       <c r="J11" t="inlineStr">
@@ -1589,35 +1589,35 @@
         <v>12000</v>
       </c>
       <c r="B12">
-        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A12)+1)))</f>
+        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A12)+1)))</f>
         <v/>
       </c>
       <c r="C12">
-        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A12)+1)))</f>
+        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A12)+1)))</f>
         <v/>
       </c>
       <c r="D12">
-        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A12)+1)))</f>
+        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A12)+1)))</f>
         <v/>
       </c>
       <c r="E12">
-        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A12)+1)))</f>
+        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A12)+1)))</f>
         <v/>
       </c>
       <c r="F12">
-        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A12)+1)))</f>
+        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A12)+1)))</f>
         <v/>
       </c>
       <c r="G12">
-        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A12)+1)))</f>
+        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A12)+1)))</f>
         <v/>
       </c>
       <c r="H12">
-        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A12)+1)))</f>
+        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A12)+1)))</f>
         <v/>
       </c>
       <c r="I12">
-        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A12)+1)))</f>
+        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A12)+1)))</f>
         <v/>
       </c>
       <c r="J12" t="inlineStr">
@@ -1635,35 +1635,35 @@
         <v>15000</v>
       </c>
       <c r="B13">
-        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A13)+1)))</f>
+        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A13)+1)))</f>
         <v/>
       </c>
       <c r="C13">
-        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A13)+1)))</f>
+        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A13)+1)))</f>
         <v/>
       </c>
       <c r="D13">
-        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A13)+1)))</f>
+        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A13)+1)))</f>
         <v/>
       </c>
       <c r="E13">
-        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A13)+1)))</f>
+        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A13)+1)))</f>
         <v/>
       </c>
       <c r="F13">
-        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A13)+1)))</f>
+        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A13)+1)))</f>
         <v/>
       </c>
       <c r="G13">
-        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A13)+1)))</f>
+        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A13)+1)))</f>
         <v/>
       </c>
       <c r="H13">
-        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A13)+1)))</f>
+        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A13)+1)))</f>
         <v/>
       </c>
       <c r="I13">
-        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A13)+1)))</f>
+        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A13)+1)))</f>
         <v/>
       </c>
       <c r="J13" t="inlineStr">
@@ -44956,35 +44956,35 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <f>IF(OR($A2="",NOT(ISNUMBER($A2)),$A2&lt;0),"",IF($A2&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A2)+1)))</f>
+        <f>IF(OR($A2="",NOT(ISNUMBER($A2)),$A2&lt;0),"",IF($A2&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A2)+1)))</f>
         <v/>
       </c>
       <c r="C2">
-        <f>IF(OR($A2="",NOT(ISNUMBER($A2)),$A2&lt;0),"",IF($A2&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A2)+1)))</f>
+        <f>IF(OR($A2="",NOT(ISNUMBER($A2)),$A2&lt;0),"",IF($A2&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A2)+1)))</f>
         <v/>
       </c>
       <c r="D2">
-        <f>IF(OR($A2="",NOT(ISNUMBER($A2)),$A2&lt;0),"",IF($A2&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A2)+1)))</f>
+        <f>IF(OR($A2="",NOT(ISNUMBER($A2)),$A2&lt;0),"",IF($A2&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A2)+1)))</f>
         <v/>
       </c>
       <c r="E2">
-        <f>IF(OR($A2="",NOT(ISNUMBER($A2)),$A2&lt;0),"",IF($A2&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A2)+1)))</f>
+        <f>IF(OR($A2="",NOT(ISNUMBER($A2)),$A2&lt;0),"",IF($A2&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A2)+1)))</f>
         <v/>
       </c>
       <c r="F2">
-        <f>IF(OR($A2="",NOT(ISNUMBER($A2)),$A2&lt;0),"",IF($A2&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A2)+1)))</f>
+        <f>IF(OR($A2="",NOT(ISNUMBER($A2)),$A2&lt;0),"",IF($A2&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A2)+1)))</f>
         <v/>
       </c>
       <c r="G2">
-        <f>IF(OR($A2="",NOT(ISNUMBER($A2)),$A2&lt;0),"",IF($A2&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A2)+1)))</f>
+        <f>IF(OR($A2="",NOT(ISNUMBER($A2)),$A2&lt;0),"",IF($A2&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A2)+1)))</f>
         <v/>
       </c>
       <c r="H2">
-        <f>IF(OR($A2="",NOT(ISNUMBER($A2)),$A2&lt;0),"",IF($A2&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A2)+1)))</f>
+        <f>IF(OR($A2="",NOT(ISNUMBER($A2)),$A2&lt;0),"",IF($A2&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A2)+1)))</f>
         <v/>
       </c>
       <c r="I2">
-        <f>IF(OR($A2="",NOT(ISNUMBER($A2)),$A2&lt;0),"",IF($A2&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A2)+1)))</f>
+        <f>IF(OR($A2="",NOT(ISNUMBER($A2)),$A2&lt;0),"",IF($A2&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A2)+1)))</f>
         <v/>
       </c>
       <c r="J2" t="inlineStr">
@@ -44998,35 +44998,35 @@
         <v>1000</v>
       </c>
       <c r="B3">
-        <f>IF(OR($A3="",NOT(ISNUMBER($A3)),$A3&lt;0),"",IF($A3&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A3)+1)))</f>
+        <f>IF(OR($A3="",NOT(ISNUMBER($A3)),$A3&lt;0),"",IF($A3&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A3)+1)))</f>
         <v/>
       </c>
       <c r="C3">
-        <f>IF(OR($A3="",NOT(ISNUMBER($A3)),$A3&lt;0),"",IF($A3&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A3)+1)))</f>
+        <f>IF(OR($A3="",NOT(ISNUMBER($A3)),$A3&lt;0),"",IF($A3&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A3)+1)))</f>
         <v/>
       </c>
       <c r="D3">
-        <f>IF(OR($A3="",NOT(ISNUMBER($A3)),$A3&lt;0),"",IF($A3&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A3)+1)))</f>
+        <f>IF(OR($A3="",NOT(ISNUMBER($A3)),$A3&lt;0),"",IF($A3&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A3)+1)))</f>
         <v/>
       </c>
       <c r="E3">
-        <f>IF(OR($A3="",NOT(ISNUMBER($A3)),$A3&lt;0),"",IF($A3&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A3)+1)))</f>
+        <f>IF(OR($A3="",NOT(ISNUMBER($A3)),$A3&lt;0),"",IF($A3&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A3)+1)))</f>
         <v/>
       </c>
       <c r="F3">
-        <f>IF(OR($A3="",NOT(ISNUMBER($A3)),$A3&lt;0),"",IF($A3&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A3)+1)))</f>
+        <f>IF(OR($A3="",NOT(ISNUMBER($A3)),$A3&lt;0),"",IF($A3&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A3)+1)))</f>
         <v/>
       </c>
       <c r="G3">
-        <f>IF(OR($A3="",NOT(ISNUMBER($A3)),$A3&lt;0),"",IF($A3&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A3)+1)))</f>
+        <f>IF(OR($A3="",NOT(ISNUMBER($A3)),$A3&lt;0),"",IF($A3&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A3)+1)))</f>
         <v/>
       </c>
       <c r="H3">
-        <f>IF(OR($A3="",NOT(ISNUMBER($A3)),$A3&lt;0),"",IF($A3&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A3)+1)))</f>
+        <f>IF(OR($A3="",NOT(ISNUMBER($A3)),$A3&lt;0),"",IF($A3&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A3)+1)))</f>
         <v/>
       </c>
       <c r="I3">
-        <f>IF(OR($A3="",NOT(ISNUMBER($A3)),$A3&lt;0),"",IF($A3&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A3)+1)))</f>
+        <f>IF(OR($A3="",NOT(ISNUMBER($A3)),$A3&lt;0),"",IF($A3&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A3)+1)))</f>
         <v/>
       </c>
       <c r="J3" t="inlineStr">
@@ -45040,35 +45040,35 @@
         <v>2000</v>
       </c>
       <c r="B4">
-        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A4)+1)))</f>
+        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A4)+1)))</f>
         <v/>
       </c>
       <c r="C4">
-        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A4)+1)))</f>
+        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A4)+1)))</f>
         <v/>
       </c>
       <c r="D4">
-        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A4)+1)))</f>
+        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A4)+1)))</f>
         <v/>
       </c>
       <c r="E4">
-        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A4)+1)))</f>
+        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A4)+1)))</f>
         <v/>
       </c>
       <c r="F4">
-        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A4)+1)))</f>
+        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A4)+1)))</f>
         <v/>
       </c>
       <c r="G4">
-        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A4)+1)))</f>
+        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A4)+1)))</f>
         <v/>
       </c>
       <c r="H4">
-        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A4)+1)))</f>
+        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A4)+1)))</f>
         <v/>
       </c>
       <c r="I4">
-        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A4)+1)))</f>
+        <f>IF(OR($A4="",NOT(ISNUMBER($A4)),$A4&lt;0),"",IF($A4&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A4)+1)))</f>
         <v/>
       </c>
       <c r="J4" t="inlineStr">
@@ -45082,35 +45082,35 @@
         <v>3000</v>
       </c>
       <c r="B5">
-        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A5)+1)))</f>
+        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A5)+1)))</f>
         <v/>
       </c>
       <c r="C5">
-        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A5)+1)))</f>
+        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A5)+1)))</f>
         <v/>
       </c>
       <c r="D5">
-        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A5)+1)))</f>
+        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A5)+1)))</f>
         <v/>
       </c>
       <c r="E5">
-        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A5)+1)))</f>
+        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A5)+1)))</f>
         <v/>
       </c>
       <c r="F5">
-        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A5)+1)))</f>
+        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A5)+1)))</f>
         <v/>
       </c>
       <c r="G5">
-        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A5)+1)))</f>
+        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A5)+1)))</f>
         <v/>
       </c>
       <c r="H5">
-        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A5)+1)))</f>
+        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A5)+1)))</f>
         <v/>
       </c>
       <c r="I5">
-        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A5)+1)))</f>
+        <f>IF(OR($A5="",NOT(ISNUMBER($A5)),$A5&lt;0),"",IF($A5&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A5)+1)))</f>
         <v/>
       </c>
       <c r="J5" t="inlineStr">
@@ -45124,35 +45124,35 @@
         <v>4000</v>
       </c>
       <c r="B6">
-        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A6)+1)))</f>
+        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A6)+1)))</f>
         <v/>
       </c>
       <c r="C6">
-        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A6)+1)))</f>
+        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A6)+1)))</f>
         <v/>
       </c>
       <c r="D6">
-        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A6)+1)))</f>
+        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A6)+1)))</f>
         <v/>
       </c>
       <c r="E6">
-        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A6)+1)))</f>
+        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A6)+1)))</f>
         <v/>
       </c>
       <c r="F6">
-        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A6)+1)))</f>
+        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A6)+1)))</f>
         <v/>
       </c>
       <c r="G6">
-        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A6)+1)))</f>
+        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A6)+1)))</f>
         <v/>
       </c>
       <c r="H6">
-        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A6)+1)))</f>
+        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A6)+1)))</f>
         <v/>
       </c>
       <c r="I6">
-        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A6)+1)))</f>
+        <f>IF(OR($A6="",NOT(ISNUMBER($A6)),$A6&lt;0),"",IF($A6&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A6)+1)))</f>
         <v/>
       </c>
       <c r="J6" t="inlineStr">
@@ -45166,35 +45166,35 @@
         <v>5000</v>
       </c>
       <c r="B7">
-        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A7)+1)))</f>
+        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A7)+1)))</f>
         <v/>
       </c>
       <c r="C7">
-        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A7)+1)))</f>
+        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A7)+1)))</f>
         <v/>
       </c>
       <c r="D7">
-        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A7)+1)))</f>
+        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A7)+1)))</f>
         <v/>
       </c>
       <c r="E7">
-        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A7)+1)))</f>
+        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A7)+1)))</f>
         <v/>
       </c>
       <c r="F7">
-        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A7)+1)))</f>
+        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A7)+1)))</f>
         <v/>
       </c>
       <c r="G7">
-        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A7)+1)))</f>
+        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A7)+1)))</f>
         <v/>
       </c>
       <c r="H7">
-        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A7)+1)))</f>
+        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A7)+1)))</f>
         <v/>
       </c>
       <c r="I7">
-        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A7)+1)))</f>
+        <f>IF(OR($A7="",NOT(ISNUMBER($A7)),$A7&lt;0),"",IF($A7&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A7)+1)))</f>
         <v/>
       </c>
       <c r="J7" t="inlineStr">
@@ -45208,35 +45208,35 @@
         <v>6000</v>
       </c>
       <c r="B8">
-        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A8)+1)))</f>
+        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A8)+1)))</f>
         <v/>
       </c>
       <c r="C8">
-        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A8)+1)))</f>
+        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A8)+1)))</f>
         <v/>
       </c>
       <c r="D8">
-        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A8)+1)))</f>
+        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A8)+1)))</f>
         <v/>
       </c>
       <c r="E8">
-        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A8)+1)))</f>
+        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A8)+1)))</f>
         <v/>
       </c>
       <c r="F8">
-        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A8)+1)))</f>
+        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A8)+1)))</f>
         <v/>
       </c>
       <c r="G8">
-        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A8)+1)))</f>
+        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A8)+1)))</f>
         <v/>
       </c>
       <c r="H8">
-        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A8)+1)))</f>
+        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A8)+1)))</f>
         <v/>
       </c>
       <c r="I8">
-        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A8)+1)))</f>
+        <f>IF(OR($A8="",NOT(ISNUMBER($A8)),$A8&lt;0),"",IF($A8&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A8)+1)))</f>
         <v/>
       </c>
       <c r="J8" t="inlineStr">
@@ -45250,35 +45250,35 @@
         <v>7000</v>
       </c>
       <c r="B9">
-        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A9)+1)))</f>
+        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A9)+1)))</f>
         <v/>
       </c>
       <c r="C9">
-        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A9)+1)))</f>
+        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A9)+1)))</f>
         <v/>
       </c>
       <c r="D9">
-        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A9)+1)))</f>
+        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A9)+1)))</f>
         <v/>
       </c>
       <c r="E9">
-        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A9)+1)))</f>
+        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A9)+1)))</f>
         <v/>
       </c>
       <c r="F9">
-        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A9)+1)))</f>
+        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A9)+1)))</f>
         <v/>
       </c>
       <c r="G9">
-        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A9)+1)))</f>
+        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A9)+1)))</f>
         <v/>
       </c>
       <c r="H9">
-        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A9)+1)))</f>
+        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A9)+1)))</f>
         <v/>
       </c>
       <c r="I9">
-        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A9)+1)))</f>
+        <f>IF(OR($A9="",NOT(ISNUMBER($A9)),$A9&lt;0),"",IF($A9&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A9)+1)))</f>
         <v/>
       </c>
       <c r="J9" t="inlineStr">
@@ -45292,35 +45292,35 @@
         <v>8000</v>
       </c>
       <c r="B10">
-        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A10)+1)))</f>
+        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A10)+1)))</f>
         <v/>
       </c>
       <c r="C10">
-        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A10)+1)))</f>
+        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A10)+1)))</f>
         <v/>
       </c>
       <c r="D10">
-        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A10)+1)))</f>
+        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A10)+1)))</f>
         <v/>
       </c>
       <c r="E10">
-        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A10)+1)))</f>
+        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A10)+1)))</f>
         <v/>
       </c>
       <c r="F10">
-        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A10)+1)))</f>
+        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A10)+1)))</f>
         <v/>
       </c>
       <c r="G10">
-        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A10)+1)))</f>
+        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A10)+1)))</f>
         <v/>
       </c>
       <c r="H10">
-        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A10)+1)))</f>
+        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A10)+1)))</f>
         <v/>
       </c>
       <c r="I10">
-        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A10)+1)))</f>
+        <f>IF(OR($A10="",NOT(ISNUMBER($A10)),$A10&lt;0),"",IF($A10&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A10)+1)))</f>
         <v/>
       </c>
       <c r="J10" t="inlineStr">
@@ -45334,35 +45334,35 @@
         <v>9000</v>
       </c>
       <c r="B11">
-        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A11)+1)))</f>
+        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A11)+1)))</f>
         <v/>
       </c>
       <c r="C11">
-        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A11)+1)))</f>
+        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A11)+1)))</f>
         <v/>
       </c>
       <c r="D11">
-        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A11)+1)))</f>
+        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A11)+1)))</f>
         <v/>
       </c>
       <c r="E11">
-        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A11)+1)))</f>
+        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A11)+1)))</f>
         <v/>
       </c>
       <c r="F11">
-        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A11)+1)))</f>
+        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A11)+1)))</f>
         <v/>
       </c>
       <c r="G11">
-        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A11)+1)))</f>
+        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A11)+1)))</f>
         <v/>
       </c>
       <c r="H11">
-        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A11)+1)))</f>
+        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A11)+1)))</f>
         <v/>
       </c>
       <c r="I11">
-        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A11)+1)))</f>
+        <f>IF(OR($A11="",NOT(ISNUMBER($A11)),$A11&lt;0),"",IF($A11&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A11)+1)))</f>
         <v/>
       </c>
       <c r="J11" t="inlineStr">
@@ -45376,35 +45376,35 @@
         <v>10000</v>
       </c>
       <c r="B12">
-        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A12)+1)))</f>
+        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A12)+1)))</f>
         <v/>
       </c>
       <c r="C12">
-        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A12)+1)))</f>
+        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A12)+1)))</f>
         <v/>
       </c>
       <c r="D12">
-        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A12)+1)))</f>
+        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A12)+1)))</f>
         <v/>
       </c>
       <c r="E12">
-        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A12)+1)))</f>
+        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A12)+1)))</f>
         <v/>
       </c>
       <c r="F12">
-        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A12)+1)))</f>
+        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A12)+1)))</f>
         <v/>
       </c>
       <c r="G12">
-        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A12)+1)))</f>
+        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A12)+1)))</f>
         <v/>
       </c>
       <c r="H12">
-        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A12)+1)))</f>
+        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A12)+1)))</f>
         <v/>
       </c>
       <c r="I12">
-        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A12)+1)))</f>
+        <f>IF(OR($A12="",NOT(ISNUMBER($A12)),$A12&lt;0),"",IF($A12&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A12)+1)))</f>
         <v/>
       </c>
       <c r="J12" t="inlineStr">
@@ -45418,35 +45418,35 @@
         <v>11000</v>
       </c>
       <c r="B13">
-        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A13)+1)))</f>
+        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A13)+1)))</f>
         <v/>
       </c>
       <c r="C13">
-        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A13)+1)))</f>
+        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A13)+1)))</f>
         <v/>
       </c>
       <c r="D13">
-        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A13)+1)))</f>
+        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A13)+1)))</f>
         <v/>
       </c>
       <c r="E13">
-        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A13)+1)))</f>
+        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A13)+1)))</f>
         <v/>
       </c>
       <c r="F13">
-        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A13)+1)))</f>
+        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A13)+1)))</f>
         <v/>
       </c>
       <c r="G13">
-        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A13)+1)))</f>
+        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A13)+1)))</f>
         <v/>
       </c>
       <c r="H13">
-        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A13)+1)))</f>
+        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A13)+1)))</f>
         <v/>
       </c>
       <c r="I13">
-        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A13)+1)))</f>
+        <f>IF(OR($A13="",NOT(ISNUMBER($A13)),$A13&lt;0),"",IF($A13&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A13)+1)))</f>
         <v/>
       </c>
       <c r="J13" t="inlineStr">
@@ -45460,35 +45460,35 @@
         <v>12000</v>
       </c>
       <c r="B14">
-        <f>IF(OR($A14="",NOT(ISNUMBER($A14)),$A14&lt;0),"",IF($A14&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A14)+1)))</f>
+        <f>IF(OR($A14="",NOT(ISNUMBER($A14)),$A14&lt;0),"",IF($A14&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A14)+1)))</f>
         <v/>
       </c>
       <c r="C14">
-        <f>IF(OR($A14="",NOT(ISNUMBER($A14)),$A14&lt;0),"",IF($A14&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A14)+1)))</f>
+        <f>IF(OR($A14="",NOT(ISNUMBER($A14)),$A14&lt;0),"",IF($A14&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A14)+1)))</f>
         <v/>
       </c>
       <c r="D14">
-        <f>IF(OR($A14="",NOT(ISNUMBER($A14)),$A14&lt;0),"",IF($A14&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A14)+1)))</f>
+        <f>IF(OR($A14="",NOT(ISNUMBER($A14)),$A14&lt;0),"",IF($A14&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A14)+1)))</f>
         <v/>
       </c>
       <c r="E14">
-        <f>IF(OR($A14="",NOT(ISNUMBER($A14)),$A14&lt;0),"",IF($A14&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A14)+1)))</f>
+        <f>IF(OR($A14="",NOT(ISNUMBER($A14)),$A14&lt;0),"",IF($A14&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A14)+1)))</f>
         <v/>
       </c>
       <c r="F14">
-        <f>IF(OR($A14="",NOT(ISNUMBER($A14)),$A14&lt;0),"",IF($A14&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A14)+1)))</f>
+        <f>IF(OR($A14="",NOT(ISNUMBER($A14)),$A14&lt;0),"",IF($A14&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A14)+1)))</f>
         <v/>
       </c>
       <c r="G14">
-        <f>IF(OR($A14="",NOT(ISNUMBER($A14)),$A14&lt;0),"",IF($A14&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A14)+1)))</f>
+        <f>IF(OR($A14="",NOT(ISNUMBER($A14)),$A14&lt;0),"",IF($A14&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A14)+1)))</f>
         <v/>
       </c>
       <c r="H14">
-        <f>IF(OR($A14="",NOT(ISNUMBER($A14)),$A14&lt;0),"",IF($A14&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A14)+1)))</f>
+        <f>IF(OR($A14="",NOT(ISNUMBER($A14)),$A14&lt;0),"",IF($A14&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A14)+1)))</f>
         <v/>
       </c>
       <c r="I14">
-        <f>IF(OR($A14="",NOT(ISNUMBER($A14)),$A14&lt;0),"",IF($A14&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A14)+1)))</f>
+        <f>IF(OR($A14="",NOT(ISNUMBER($A14)),$A14&lt;0),"",IF($A14&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A14)+1)))</f>
         <v/>
       </c>
       <c r="J14" t="inlineStr">
@@ -45502,35 +45502,35 @@
         <v>13000</v>
       </c>
       <c r="B15">
-        <f>IF(OR($A15="",NOT(ISNUMBER($A15)),$A15&lt;0),"",IF($A15&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A15)+1)))</f>
+        <f>IF(OR($A15="",NOT(ISNUMBER($A15)),$A15&lt;0),"",IF($A15&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A15)+1)))</f>
         <v/>
       </c>
       <c r="C15">
-        <f>IF(OR($A15="",NOT(ISNUMBER($A15)),$A15&lt;0),"",IF($A15&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A15)+1)))</f>
+        <f>IF(OR($A15="",NOT(ISNUMBER($A15)),$A15&lt;0),"",IF($A15&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A15)+1)))</f>
         <v/>
       </c>
       <c r="D15">
-        <f>IF(OR($A15="",NOT(ISNUMBER($A15)),$A15&lt;0),"",IF($A15&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A15)+1)))</f>
+        <f>IF(OR($A15="",NOT(ISNUMBER($A15)),$A15&lt;0),"",IF($A15&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A15)+1)))</f>
         <v/>
       </c>
       <c r="E15">
-        <f>IF(OR($A15="",NOT(ISNUMBER($A15)),$A15&lt;0),"",IF($A15&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A15)+1)))</f>
+        <f>IF(OR($A15="",NOT(ISNUMBER($A15)),$A15&lt;0),"",IF($A15&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A15)+1)))</f>
         <v/>
       </c>
       <c r="F15">
-        <f>IF(OR($A15="",NOT(ISNUMBER($A15)),$A15&lt;0),"",IF($A15&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A15)+1)))</f>
+        <f>IF(OR($A15="",NOT(ISNUMBER($A15)),$A15&lt;0),"",IF($A15&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A15)+1)))</f>
         <v/>
       </c>
       <c r="G15">
-        <f>IF(OR($A15="",NOT(ISNUMBER($A15)),$A15&lt;0),"",IF($A15&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A15)+1)))</f>
+        <f>IF(OR($A15="",NOT(ISNUMBER($A15)),$A15&lt;0),"",IF($A15&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A15)+1)))</f>
         <v/>
       </c>
       <c r="H15">
-        <f>IF(OR($A15="",NOT(ISNUMBER($A15)),$A15&lt;0),"",IF($A15&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A15)+1)))</f>
+        <f>IF(OR($A15="",NOT(ISNUMBER($A15)),$A15&lt;0),"",IF($A15&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A15)+1)))</f>
         <v/>
       </c>
       <c r="I15">
-        <f>IF(OR($A15="",NOT(ISNUMBER($A15)),$A15&lt;0),"",IF($A15&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A15)+1)))</f>
+        <f>IF(OR($A15="",NOT(ISNUMBER($A15)),$A15&lt;0),"",IF($A15&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A15)+1)))</f>
         <v/>
       </c>
       <c r="J15" t="inlineStr">
@@ -45544,35 +45544,35 @@
         <v>14000</v>
       </c>
       <c r="B16">
-        <f>IF(OR($A16="",NOT(ISNUMBER($A16)),$A16&lt;0),"",IF($A16&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A16)+1)))</f>
+        <f>IF(OR($A16="",NOT(ISNUMBER($A16)),$A16&lt;0),"",IF($A16&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A16)+1)))</f>
         <v/>
       </c>
       <c r="C16">
-        <f>IF(OR($A16="",NOT(ISNUMBER($A16)),$A16&lt;0),"",IF($A16&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A16)+1)))</f>
+        <f>IF(OR($A16="",NOT(ISNUMBER($A16)),$A16&lt;0),"",IF($A16&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A16)+1)))</f>
         <v/>
       </c>
       <c r="D16">
-        <f>IF(OR($A16="",NOT(ISNUMBER($A16)),$A16&lt;0),"",IF($A16&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A16)+1)))</f>
+        <f>IF(OR($A16="",NOT(ISNUMBER($A16)),$A16&lt;0),"",IF($A16&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A16)+1)))</f>
         <v/>
       </c>
       <c r="E16">
-        <f>IF(OR($A16="",NOT(ISNUMBER($A16)),$A16&lt;0),"",IF($A16&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A16)+1)))</f>
+        <f>IF(OR($A16="",NOT(ISNUMBER($A16)),$A16&lt;0),"",IF($A16&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A16)+1)))</f>
         <v/>
       </c>
       <c r="F16">
-        <f>IF(OR($A16="",NOT(ISNUMBER($A16)),$A16&lt;0),"",IF($A16&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A16)+1)))</f>
+        <f>IF(OR($A16="",NOT(ISNUMBER($A16)),$A16&lt;0),"",IF($A16&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A16)+1)))</f>
         <v/>
       </c>
       <c r="G16">
-        <f>IF(OR($A16="",NOT(ISNUMBER($A16)),$A16&lt;0),"",IF($A16&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A16)+1)))</f>
+        <f>IF(OR($A16="",NOT(ISNUMBER($A16)),$A16&lt;0),"",IF($A16&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A16)+1)))</f>
         <v/>
       </c>
       <c r="H16">
-        <f>IF(OR($A16="",NOT(ISNUMBER($A16)),$A16&lt;0),"",IF($A16&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A16)+1)))</f>
+        <f>IF(OR($A16="",NOT(ISNUMBER($A16)),$A16&lt;0),"",IF($A16&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A16)+1)))</f>
         <v/>
       </c>
       <c r="I16">
-        <f>IF(OR($A16="",NOT(ISNUMBER($A16)),$A16&lt;0),"",IF($A16&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A16)+1)))</f>
+        <f>IF(OR($A16="",NOT(ISNUMBER($A16)),$A16&lt;0),"",IF($A16&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A16)+1)))</f>
         <v/>
       </c>
       <c r="J16" t="inlineStr">
@@ -45586,35 +45586,35 @@
         <v>15000</v>
       </c>
       <c r="B17">
-        <f>IF(OR($A17="",NOT(ISNUMBER($A17)),$A17&lt;0),"",IF($A17&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A17)+1)))</f>
+        <f>IF(OR($A17="",NOT(ISNUMBER($A17)),$A17&lt;0),"",IF($A17&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A17)+1)))</f>
         <v/>
       </c>
       <c r="C17">
-        <f>IF(OR($A17="",NOT(ISNUMBER($A17)),$A17&lt;0),"",IF($A17&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A17)+1)))</f>
+        <f>IF(OR($A17="",NOT(ISNUMBER($A17)),$A17&lt;0),"",IF($A17&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A17)+1)))</f>
         <v/>
       </c>
       <c r="D17">
-        <f>IF(OR($A17="",NOT(ISNUMBER($A17)),$A17&lt;0),"",IF($A17&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A17)+1)))</f>
+        <f>IF(OR($A17="",NOT(ISNUMBER($A17)),$A17&lt;0),"",IF($A17&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A17)+1)))</f>
         <v/>
       </c>
       <c r="E17">
-        <f>IF(OR($A17="",NOT(ISNUMBER($A17)),$A17&lt;0),"",IF($A17&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A17)+1)))</f>
+        <f>IF(OR($A17="",NOT(ISNUMBER($A17)),$A17&lt;0),"",IF($A17&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A17)+1)))</f>
         <v/>
       </c>
       <c r="F17">
-        <f>IF(OR($A17="",NOT(ISNUMBER($A17)),$A17&lt;0),"",IF($A17&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A17)+1)))</f>
+        <f>IF(OR($A17="",NOT(ISNUMBER($A17)),$A17&lt;0),"",IF($A17&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A17)+1)))</f>
         <v/>
       </c>
       <c r="G17">
-        <f>IF(OR($A17="",NOT(ISNUMBER($A17)),$A17&lt;0),"",IF($A17&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A17)+1)))</f>
+        <f>IF(OR($A17="",NOT(ISNUMBER($A17)),$A17&lt;0),"",IF($A17&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A17)+1)))</f>
         <v/>
       </c>
       <c r="H17">
-        <f>IF(OR($A17="",NOT(ISNUMBER($A17)),$A17&lt;0),"",IF($A17&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A17)+1)))</f>
+        <f>IF(OR($A17="",NOT(ISNUMBER($A17)),$A17&lt;0),"",IF($A17&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A17)+1)))</f>
         <v/>
       </c>
       <c r="I17">
-        <f>IF(OR($A17="",NOT(ISNUMBER($A17)),$A17&lt;0),"",IF($A17&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A17)+1)))</f>
+        <f>IF(OR($A17="",NOT(ISNUMBER($A17)),$A17&lt;0),"",IF($A17&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A17)+1)))</f>
         <v/>
       </c>
       <c r="J17" t="inlineStr">
@@ -45628,35 +45628,35 @@
         <v>17000</v>
       </c>
       <c r="B18">
-        <f>IF(OR($A18="",NOT(ISNUMBER($A18)),$A18&lt;0),"",IF($A18&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A18)+1)))</f>
+        <f>IF(OR($A18="",NOT(ISNUMBER($A18)),$A18&lt;0),"",IF($A18&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A18)+1)))</f>
         <v/>
       </c>
       <c r="C18">
-        <f>IF(OR($A18="",NOT(ISNUMBER($A18)),$A18&lt;0),"",IF($A18&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A18)+1)))</f>
+        <f>IF(OR($A18="",NOT(ISNUMBER($A18)),$A18&lt;0),"",IF($A18&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A18)+1)))</f>
         <v/>
       </c>
       <c r="D18">
-        <f>IF(OR($A18="",NOT(ISNUMBER($A18)),$A18&lt;0),"",IF($A18&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A18)+1)))</f>
+        <f>IF(OR($A18="",NOT(ISNUMBER($A18)),$A18&lt;0),"",IF($A18&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A18)+1)))</f>
         <v/>
       </c>
       <c r="E18">
-        <f>IF(OR($A18="",NOT(ISNUMBER($A18)),$A18&lt;0),"",IF($A18&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A18)+1)))</f>
+        <f>IF(OR($A18="",NOT(ISNUMBER($A18)),$A18&lt;0),"",IF($A18&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A18)+1)))</f>
         <v/>
       </c>
       <c r="F18">
-        <f>IF(OR($A18="",NOT(ISNUMBER($A18)),$A18&lt;0),"",IF($A18&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A18)+1)))</f>
+        <f>IF(OR($A18="",NOT(ISNUMBER($A18)),$A18&lt;0),"",IF($A18&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A18)+1)))</f>
         <v/>
       </c>
       <c r="G18">
-        <f>IF(OR($A18="",NOT(ISNUMBER($A18)),$A18&lt;0),"",IF($A18&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A18)+1)))</f>
+        <f>IF(OR($A18="",NOT(ISNUMBER($A18)),$A18&lt;0),"",IF($A18&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A18)+1)))</f>
         <v/>
       </c>
       <c r="H18">
-        <f>IF(OR($A18="",NOT(ISNUMBER($A18)),$A18&lt;0),"",IF($A18&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A18)+1)))</f>
+        <f>IF(OR($A18="",NOT(ISNUMBER($A18)),$A18&lt;0),"",IF($A18&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A18)+1)))</f>
         <v/>
       </c>
       <c r="I18">
-        <f>IF(OR($A18="",NOT(ISNUMBER($A18)),$A18&lt;0),"",IF($A18&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A18)+1)))</f>
+        <f>IF(OR($A18="",NOT(ISNUMBER($A18)),$A18&lt;0),"",IF($A18&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A18)+1)))</f>
         <v/>
       </c>
       <c r="J18" t="inlineStr">
@@ -45670,35 +45670,35 @@
         <v>18000</v>
       </c>
       <c r="B19">
-        <f>IF(OR($A19="",NOT(ISNUMBER($A19)),$A19&lt;0),"",IF($A19&gt;할인율표!$E$16,"할인 없음(최대 초과)",INDEX(할인율표!$G$2:$G$16,COUNTIF(할인율표!$E$2:$E$16,"&lt;"&amp;$A19)+1)))</f>
+        <f>IF(OR($A19="",NOT(ISNUMBER($A19)),$A19&lt;0),"",IF($A19&gt;'할인율표'!$E$16,"할인 없음(최대 초과)",INDEX('할인율표'!$G$2:$G$16,COUNTIF('할인율표'!$E$2:$E$16,"&lt;"&amp;$A19)+1)))</f>
         <v/>
       </c>
       <c r="C19">
-        <f>IF(OR($A19="",NOT(ISNUMBER($A19)),$A19&lt;0),"",IF($A19&gt;할인율표!$E$46,"할인 없음(최대 초과)",INDEX(할인율표!$G$32:$G$46,COUNTIF(할인율표!$E$32:$E$46,"&lt;"&amp;$A19)+1)))</f>
+        <f>IF(OR($A19="",NOT(ISNUMBER($A19)),$A19&lt;0),"",IF($A19&gt;'할인율표'!$E$46,"할인 없음(최대 초과)",INDEX('할인율표'!$G$32:$G$46,COUNTIF('할인율표'!$E$32:$E$46,"&lt;"&amp;$A19)+1)))</f>
         <v/>
       </c>
       <c r="D19">
-        <f>IF(OR($A19="",NOT(ISNUMBER($A19)),$A19&lt;0),"",IF($A19&gt;할인율표!$E$128,"할인 없음(최대 초과)",INDEX(할인율표!$G$122:$G$128,COUNTIF(할인율표!$E$122:$E$128,"&lt;"&amp;$A19)+1)))</f>
+        <f>IF(OR($A19="",NOT(ISNUMBER($A19)),$A19&lt;0),"",IF($A19&gt;'할인율표'!$E$128,"할인 없음(최대 초과)",INDEX('할인율표'!$G$122:$G$128,COUNTIF('할인율표'!$E$122:$E$128,"&lt;"&amp;$A19)+1)))</f>
         <v/>
       </c>
       <c r="E19">
-        <f>IF(OR($A19="",NOT(ISNUMBER($A19)),$A19&lt;0),"",IF($A19&gt;할인율표!$E$189,"할인 없음(최대 초과)",INDEX(할인율표!$G$178:$G$189,COUNTIF(할인율표!$E$178:$E$189,"&lt;"&amp;$A19)+1)))</f>
+        <f>IF(OR($A19="",NOT(ISNUMBER($A19)),$A19&lt;0),"",IF($A19&gt;'할인율표'!$E$189,"할인 없음(최대 초과)",INDEX('할인율표'!$G$178:$G$189,COUNTIF('할인율표'!$E$178:$E$189,"&lt;"&amp;$A19)+1)))</f>
         <v/>
       </c>
       <c r="F19">
-        <f>IF(OR($A19="",NOT(ISNUMBER($A19)),$A19&lt;0),"",IF($A19&gt;할인율표!$E$432,"할인 없음(최대 초과)",INDEX(할인율표!$G$424:$G$432,COUNTIF(할인율표!$E$424:$E$432,"&lt;"&amp;$A19)+1)))</f>
+        <f>IF(OR($A19="",NOT(ISNUMBER($A19)),$A19&lt;0),"",IF($A19&gt;'할인율표'!$E$432,"할인 없음(최대 초과)",INDEX('할인율표'!$G$424:$G$432,COUNTIF('할인율표'!$E$424:$E$432,"&lt;"&amp;$A19)+1)))</f>
         <v/>
       </c>
       <c r="G19">
-        <f>IF(OR($A19="",NOT(ISNUMBER($A19)),$A19&lt;0),"",IF($A19&gt;할인율표!$E$457,"할인 없음(최대 초과)",INDEX(할인율표!$G$451:$G$457,COUNTIF(할인율표!$E$451:$E$457,"&lt;"&amp;$A19)+1)))</f>
+        <f>IF(OR($A19="",NOT(ISNUMBER($A19)),$A19&lt;0),"",IF($A19&gt;'할인율표'!$E$457,"할인 없음(최대 초과)",INDEX('할인율표'!$G$451:$G$457,COUNTIF('할인율표'!$E$451:$E$457,"&lt;"&amp;$A19)+1)))</f>
         <v/>
       </c>
       <c r="H19">
-        <f>IF(OR($A19="",NOT(ISNUMBER($A19)),$A19&lt;0),"",IF($A19&gt;할인율표!$E$465,"할인 없음(최대 초과)",INDEX(할인율표!$G$458:$G$465,COUNTIF(할인율표!$E$458:$E$465,"&lt;"&amp;$A19)+1)))</f>
+        <f>IF(OR($A19="",NOT(ISNUMBER($A19)),$A19&lt;0),"",IF($A19&gt;'할인율표'!$E$465,"할인 없음(최대 초과)",INDEX('할인율표'!$G$458:$G$465,COUNTIF('할인율표'!$E$458:$E$465,"&lt;"&amp;$A19)+1)))</f>
         <v/>
       </c>
       <c r="I19">
-        <f>IF(OR($A19="",NOT(ISNUMBER($A19)),$A19&lt;0),"",IF($A19&gt;할인율표!$E$488,"할인 없음(최대 초과)",INDEX(할인율표!$G$474:$G$488,COUNTIF(할인율표!$E$474:$E$488,"&lt;"&amp;$A19)+1)))</f>
+        <f>IF(OR($A19="",NOT(ISNUMBER($A19)),$A19&lt;0),"",IF($A19&gt;'할인율표'!$E$488,"할인 없음(최대 초과)",INDEX('할인율표'!$G$474:$G$488,COUNTIF('할인율표'!$E$474:$E$488,"&lt;"&amp;$A19)+1)))</f>
         <v/>
       </c>
       <c r="J19" t="inlineStr">
